--- a/data-raw/data-tidy/public-site/moa-genetic-resource/xlsx/list-year-2025-batch-04.xlsx
+++ b/data-raw/data-tidy/public-site/moa-genetic-resource/xlsx/list-year-2025-batch-04.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30228"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\github\techme\data-raw\public-site\moa-genetic-resource\xlsx\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\github\techme\data-raw\data-tidy\public-site\moa-genetic-resource\xlsx\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B3E5AA4F-D5A8-4CE1-8BE3-FC6672D8CAD8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C5DF7C40-A0C2-4F37-9AF2-BD756EBA87CC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="51480" yWindow="5070" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet 1" sheetId="1" r:id="rId1"/>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="57" uniqueCount="40">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="57" uniqueCount="41">
   <si>
     <t>year</t>
   </si>
@@ -85,10 +85,6 @@
   </si>
   <si>
     <t>甘肃</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>畜禽</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
@@ -171,6 +167,14 @@
   </si>
   <si>
     <t>广东</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>畜禽保种场</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>畜禽基因库</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -642,22 +646,22 @@
         <v>2025</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>20</v>
+        <v>40</v>
       </c>
       <c r="D5">
         <v>1</v>
       </c>
       <c r="E5" t="s">
+        <v>22</v>
+      </c>
+      <c r="F5" t="s">
         <v>23</v>
       </c>
-      <c r="F5" t="s">
-        <v>24</v>
-      </c>
       <c r="G5" s="2" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.25">
@@ -665,22 +669,22 @@
         <v>2025</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>20</v>
+        <v>39</v>
       </c>
       <c r="D6">
         <v>2</v>
       </c>
       <c r="E6" t="s">
+        <v>24</v>
+      </c>
+      <c r="F6" t="s">
         <v>25</v>
       </c>
-      <c r="F6" t="s">
-        <v>26</v>
-      </c>
       <c r="G6" s="2" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.25">
@@ -688,22 +692,22 @@
         <v>2025</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>20</v>
+        <v>40</v>
       </c>
       <c r="D7">
         <v>3</v>
       </c>
       <c r="E7" t="s">
+        <v>26</v>
+      </c>
+      <c r="F7" t="s">
         <v>27</v>
       </c>
-      <c r="F7" t="s">
-        <v>28</v>
-      </c>
       <c r="G7" s="2" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
     </row>
     <row r="8" spans="1:7" x14ac:dyDescent="0.25">
@@ -711,19 +715,19 @@
         <v>2025</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>20</v>
+        <v>40</v>
       </c>
       <c r="D8">
         <v>4</v>
       </c>
       <c r="E8" t="s">
+        <v>28</v>
+      </c>
+      <c r="F8" t="s">
         <v>29</v>
-      </c>
-      <c r="F8" t="s">
-        <v>30</v>
       </c>
       <c r="G8" s="2" t="s">
         <v>8</v>
@@ -734,22 +738,22 @@
         <v>2025</v>
       </c>
       <c r="B9" s="3" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>20</v>
+        <v>40</v>
       </c>
       <c r="D9">
         <v>5</v>
       </c>
       <c r="E9" t="s">
+        <v>30</v>
+      </c>
+      <c r="F9" s="1" t="s">
         <v>31</v>
       </c>
-      <c r="F9" s="1" t="s">
-        <v>32</v>
-      </c>
       <c r="G9" s="2" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
     </row>
     <row r="10" spans="1:7" x14ac:dyDescent="0.25">
@@ -757,19 +761,19 @@
         <v>2025</v>
       </c>
       <c r="B10" s="3" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>20</v>
+        <v>39</v>
       </c>
       <c r="D10">
         <v>6</v>
       </c>
       <c r="E10" t="s">
+        <v>32</v>
+      </c>
+      <c r="F10" t="s">
         <v>33</v>
-      </c>
-      <c r="F10" t="s">
-        <v>34</v>
       </c>
       <c r="G10" s="2" t="s">
         <v>18</v>
@@ -780,19 +784,19 @@
         <v>2025</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>20</v>
+        <v>40</v>
       </c>
       <c r="D11">
         <v>7</v>
       </c>
       <c r="E11" t="s">
+        <v>34</v>
+      </c>
+      <c r="F11" t="s">
         <v>35</v>
-      </c>
-      <c r="F11" t="s">
-        <v>36</v>
       </c>
       <c r="G11" s="2" t="s">
         <v>9</v>
